--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>45870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45413</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44995</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>45078</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44585</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>44904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44515</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44995</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45238</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45603</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>45013</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45098</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>44719</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45881</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45016</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44543</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45474</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>44995</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44727</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45870</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45520</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>44817</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45441</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>45714</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>45398</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45859</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45604</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>45690</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44817</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>46241</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45442</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>46073</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45986</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>45896</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46206</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>46006</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>45520</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44699</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44698</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45411</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44917</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>46093</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45078</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45989</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46150</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46149</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>45842</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>46156</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45252</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>46280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45044</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>46286</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45576</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>44488</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44663</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>44860</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44698</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>44543</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>44473</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44673</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44732</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44466</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>44515</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44652</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44466</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>44473</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>44677</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44782</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44500</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44886</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44851</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44860</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44473</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44679</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44743</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44585</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45219</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45042</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>45429</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45467</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45474</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45918</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44581</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44543</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44966</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45400</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>45397</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44595</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46034</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45888</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>46036</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45572</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45890</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46042</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45558</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45411</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45898</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45898</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45903</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44867</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45565</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45908</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>44635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45607</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45915</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45915</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45915</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46063</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46066</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>46069</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>46069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>46069</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46069</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>46069</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>46071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>46072</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46072</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>46073</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46073</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45805</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45496</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>46085</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45805</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45810</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45810</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44671</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>46085</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46090</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>46090</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45761</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46093</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44481</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46097</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45943</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45943</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45943</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46101</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45946</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45947</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45952</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45947</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44746</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45294</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46113</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45609</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45582</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45183</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45611</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45604</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45992</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45992</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44966</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45611</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45582</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>44995</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45968</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45971</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>44480</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>44480</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45461</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45531</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45980</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45980</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45979</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45979</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>46134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>46134</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45985</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>46136</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45593</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>46135</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45993</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45994</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45593</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45308</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45994</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>46000</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>46000</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>46000</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>46000</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45999</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45999</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45635</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45545</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45631</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45461</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45917</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45852</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>46008</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45397</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45860</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45497</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>44867</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45168</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44601</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44543</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45049</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45520</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>45016</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>46091</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>44596</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45635</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>46148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44809</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45474</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45107</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45835</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45835</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45561</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45839</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45104</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>46162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45953</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>46162</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>46168</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45860</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45520</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44543</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45461</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>46160</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>44480</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>46181</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>46181</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>46182</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>46182</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>46182</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45874</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>46188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45874</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45874</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45874</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46191</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>46191</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45874</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45876</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45875</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45783</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>46197</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45400</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44580</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46203</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45219</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>46206</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46057</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46206</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>46206</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>46206</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>46206</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>46206</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>46206</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>46156</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>44650</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>46255</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46255</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>46255</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46255</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44648</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>46255</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45561</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46255</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44685</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>46219</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>46262</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>46262</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45180</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45155</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>44904</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>46223</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44844</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>44845</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44748</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45196</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45302</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45014</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>46274</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45467</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44844</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>46237</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>46279</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>46279</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>46279</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45462</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45522</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>46282</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>46282</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>46282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>46240</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>46240</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>46241</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44776</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45553</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44867</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>46240</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>46283</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>46241</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>46241</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>46241</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>46246</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46148</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44650</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44665</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45335</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45868</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44966</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>44858</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45239</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45242</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45077</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45660</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45364</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>45520</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44904</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45242</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45271</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45260</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44712</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44543</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45551</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>44972</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44998</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44998</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>44998</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45258</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>44566</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>44607</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45133</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>45870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45413</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44995</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>45078</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44585</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>44904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44515</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44995</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45238</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45603</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>45013</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45098</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>44719</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45881</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45016</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44543</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45474</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>44995</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44727</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45870</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45520</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>44817</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45441</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>45714</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>45398</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45859</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45604</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>45690</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44817</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>46241</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45442</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>46073</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45986</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>45896</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46206</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>46006</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>45520</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44699</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44698</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45411</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44917</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>46093</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45078</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45989</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46150</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46149</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>45842</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>46156</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45252</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>46280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45044</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>46286</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45576</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>44488</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44663</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>44860</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44698</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>44543</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>44473</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44673</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44732</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44466</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>44515</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44652</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44466</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>44473</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>44677</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44782</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44500</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44886</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44851</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44860</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44473</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44679</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44743</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44585</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45219</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45042</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>45429</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45467</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45474</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45918</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44581</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44543</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44966</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45400</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>45397</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44595</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46034</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45888</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>46036</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45572</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45890</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46042</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45558</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45411</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45898</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45898</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45903</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44867</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45565</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45908</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>44635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45607</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45915</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45915</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45915</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46063</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46066</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>46069</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>46069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>46069</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46069</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>46069</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>46071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>46072</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46072</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>46073</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46073</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45805</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45929</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45496</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>46085</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45805</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45810</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45810</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44671</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>46085</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46090</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>46090</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45761</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46093</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44481</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46097</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45943</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45943</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45943</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46101</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45946</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45947</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45952</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45947</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44746</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45294</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46113</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45609</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45582</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45183</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45611</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45604</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45992</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45992</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44966</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45611</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45582</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>44995</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45968</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45971</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>44480</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>44480</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45461</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>45531</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>45980</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>45980</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45979</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45979</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>46134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>46134</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45985</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>46136</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45593</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>46135</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45993</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45994</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45593</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45308</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45994</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>46000</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>46000</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>46000</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>46000</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45999</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45999</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45635</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45545</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45631</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45461</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45917</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45852</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>46008</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45397</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45860</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45497</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>44867</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45168</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44601</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44543</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45049</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45520</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>45016</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>46091</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>44596</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45635</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>46148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44809</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45474</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45107</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45835</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45835</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45561</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45839</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45104</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>46162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45953</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>46162</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>46168</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45860</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45520</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44543</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45461</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>46160</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>44480</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>46181</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>46181</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>46182</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>46182</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>46182</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45874</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>46188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45874</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45874</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45874</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46191</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>46191</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45874</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45876</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45875</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45783</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>46197</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45400</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44580</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46203</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45219</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>46206</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46057</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46206</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>46206</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>46206</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>46206</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>46206</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>46206</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>46156</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>44650</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>46255</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>46255</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>46255</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46255</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44648</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>46255</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45561</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46255</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44685</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>46219</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>46262</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>46262</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45180</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45155</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>44904</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>46223</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44844</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>44845</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44748</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45196</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45302</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45014</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>46274</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45467</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44844</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>46237</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>46279</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>46279</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>46279</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45462</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45522</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>46282</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>46282</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>46282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>46240</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>46240</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>46241</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44776</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45553</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44867</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>46240</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>46283</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>46241</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>46241</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>46241</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>46246</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>46148</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44650</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44665</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>45335</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45868</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44966</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>44858</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45239</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45242</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45077</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45660</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45364</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>45520</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44904</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45242</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45271</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45260</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44712</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44543</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45551</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>44972</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44998</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>44998</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>44998</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45258</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>44566</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>44607</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45133</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>45870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45413</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44995</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>45078</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44585</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>44904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44515</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44995</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45238</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45603</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>45520</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>45013</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45098</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45156</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>44543</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44719</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45881</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45233</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45016</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44543</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45474</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44995</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44727</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>46290</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45870</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44585</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>45714</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>45441</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45398</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>46255</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45604</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45690</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45859</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44817</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>46241</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>46002</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46073</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45986</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45903</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45896</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44817</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>46206</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45196</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44699</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45442</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45106</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>46294</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>46006</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45520</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45411</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>45044</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45810</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>46093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45989</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45842</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45576</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45252</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46149</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44917</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45078</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>46156</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>46280</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45219</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44650</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44950</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>45602</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46286</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>46297</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>46255</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45720</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44663</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44860</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44698</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44543</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44846</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44473</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44673</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44732</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>44515</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>44652</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>44473</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44782</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44500</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44886</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44851</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44860</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44473</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44743</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>44580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44585</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45429</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44601</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44966</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>44966</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44543</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45561</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45260</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45660</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44543</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45635</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45474</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45631</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>46008</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45183</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45258</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44648</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45572</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45890</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45898</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46034</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45898</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45898</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44543</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45903</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>46036</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45908</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45411</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>46042</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45400</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45397</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45915</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44665</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45915</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45915</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>44867</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45558</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45565</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45805</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45364</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45461</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44844</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45607</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44635</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>46063</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>46069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>46069</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46066</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>46069</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>46069</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44480</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46073</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>46073</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46072</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>46072</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45943</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45943</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44858</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45810</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45947</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44543</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45302</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>46085</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>46085</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45294</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>44995</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46090</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44809</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>46090</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45604</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45183</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45098</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>45271</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45611</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45611</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>45531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>46093</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45561</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46097</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45968</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>46101</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45952</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46048</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46101</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45979</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45980</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45980</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45980</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45537</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45985</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45985</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45985</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>46113</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45593</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45992</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45992</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45993</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45593</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45994</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45994</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45999</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45999</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>46000</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45180</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46000</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>46000</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46000</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>46135</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46134</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46134</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45461</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45467</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>44776</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45835</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45835</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45860</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45239</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45545</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>46136</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45104</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45839</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45852</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45842</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>46136</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45917</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44596</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45219</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45635</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45497</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45242</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45860</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45016</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45939</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45397</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45520</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45308</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45461</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45522</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44481</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46091</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44595</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46148</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45474</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45874</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45874</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45874</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45875</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45874</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45874</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>46162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>46162</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45876</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>46168</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>44671</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46160</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45219</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>46182</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>46181</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>46181</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>46182</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44581</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>46182</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44480</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45520</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45520</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>44650</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46191</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46191</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45783</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46197</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45042</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44867</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>46203</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46203</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46205</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>44746</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46206</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>46206</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>46206</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46206</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>46206</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46206</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46206</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46206</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>46156</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45155</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>46219</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>46262</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46262</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45077</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>45553</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>46223</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45582</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>45582</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45170</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45496</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45196</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>45196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>46274</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>46279</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>46237</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46279</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>46279</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45107</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45462</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45467</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46240</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>46240</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>46240</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>46282</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>46282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46148</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>46241</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>46241</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>46241</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>46241</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>46282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>46246</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45014</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45868</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46293</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46293</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>46293</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>46293</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>46293</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>46293</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>46293</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45335</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>44845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45551</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44650</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>46255</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>46255</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>46255</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45400</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>46057</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>44844</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>46255</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>46255</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44580</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>45049</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44904</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45609</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45242</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44867</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>44748</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45761</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45013</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45168</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44480</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44998</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44998</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44998</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44566</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45133</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>44607</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45923</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>45870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45413</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44995</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>45078</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44585</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>44904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44515</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44995</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45238</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45603</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>45520</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>45013</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45098</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45156</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>44543</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>44719</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45881</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45233</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45016</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44543</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45474</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44995</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44727</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>46290</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45870</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44585</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>44817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>45714</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>45441</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45398</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>46255</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45604</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45690</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45859</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44817</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>46241</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>46002</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46073</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45986</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45903</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45896</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44817</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>46206</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45196</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44699</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45442</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45106</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>46294</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>46006</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45520</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45411</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>45044</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45810</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>46093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45989</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45842</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45576</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45252</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46149</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44917</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45078</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>46156</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>46280</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45219</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44650</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44950</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>45602</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46286</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>46297</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>46255</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45720</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44663</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44860</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44698</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44543</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44846</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44473</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44673</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44732</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>44515</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>44652</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>44473</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44782</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44500</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44886</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44851</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44860</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44473</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44743</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>44580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44585</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45429</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44601</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44966</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>44966</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44543</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45561</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45260</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45660</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44543</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45635</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45474</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45631</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>46008</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45183</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45258</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44648</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45572</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45890</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45898</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46034</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45898</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45898</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44543</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45903</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>46036</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45908</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45411</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>46042</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45400</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45397</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45915</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44665</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45915</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45915</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>44867</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45558</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45565</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45805</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45805</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45364</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45461</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44844</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45607</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44635</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>46063</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>46069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>46069</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46066</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>46069</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>46069</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44480</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46069</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46073</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>46073</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46072</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>46072</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45943</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45943</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44858</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45810</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45947</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44543</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45302</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>46085</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>46085</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45294</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>44995</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46090</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44809</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>46090</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45604</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45183</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45098</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>45271</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45611</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45611</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>45531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>46093</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45561</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46097</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45968</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>46101</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45952</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46048</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46101</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45979</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45979</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45980</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45980</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45980</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45537</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45985</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45985</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45985</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>46113</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45593</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45992</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45992</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45993</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45593</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45994</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45994</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45999</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45999</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>46000</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45180</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46000</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>46000</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46000</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>46135</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46134</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46134</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45461</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45467</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>44776</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45835</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45835</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45860</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45239</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45545</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>46136</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45104</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45839</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45852</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45842</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>46136</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45917</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44596</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45219</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45635</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45497</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45242</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45860</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45016</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45939</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45397</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45520</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45308</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45461</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45522</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44481</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46091</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44595</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46148</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45474</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45874</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45874</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45874</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45875</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45874</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45874</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>46162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>46162</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45876</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>46168</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>44671</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46160</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45219</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>46182</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>46181</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>46181</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>46182</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44581</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>46182</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44480</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45520</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45520</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>46188</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>44650</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46191</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46191</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45783</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46197</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45042</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44867</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>46203</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>46203</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46205</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>44746</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46206</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>46206</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>46206</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46206</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>46206</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46206</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46206</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46206</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>46156</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45155</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>46219</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>46262</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46262</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45077</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>45553</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>46223</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45582</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>45582</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45170</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45496</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45196</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>45196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>46274</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>46279</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>46237</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46279</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>46279</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45107</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45462</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45467</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46240</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>46240</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>46240</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>46282</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>46282</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46148</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>46241</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>46241</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>46241</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>46241</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>46282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>46246</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45014</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45868</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46293</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46293</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>46293</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>46293</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>46293</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>46293</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>46293</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45335</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>44845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45551</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44650</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>46255</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>46255</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>46255</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45400</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>46057</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>44844</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>46255</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>46255</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44580</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>45049</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44904</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45609</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45242</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44867</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>44748</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45761</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45013</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45168</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44480</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44998</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44998</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44998</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44566</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45133</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>44607</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45870</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>45923</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45413</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45078</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>44585</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>44904</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44515</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44995</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45635</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45873</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45238</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45603</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45520</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45013</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45098</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44719</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45016</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45881</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44543</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>44995</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>45474</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44727</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>46290</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>46261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44585</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45870</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44788</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45441</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45714</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45398</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45055</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45259</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>46255</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>45859</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45690</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45604</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44817</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>46241</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45442</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45986</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45520</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45903</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>46073</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45896</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>45874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44817</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>46206</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>46006</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>46294</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44860</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45411</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45576</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44917</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>45602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44650</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45842</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45078</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45252</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45989</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45044</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>44950</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>46150</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>46149</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>46093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46280</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46297</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>46156</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45720</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44663</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44698</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44543</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44846</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44673</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44732</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44679</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44515</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44652</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44743</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44886</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44677</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44851</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>44860</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44580</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44585</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45077</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45660</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45429</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45042</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45107</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>45364</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45520</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45561</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45242</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45104</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45271</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45260</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45467</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45474</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44581</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>44543</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44966</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45520</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44543</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45572</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44543</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>44595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45551</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45890</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45898</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45898</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45898</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45898</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45898</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>45461</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45908</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44480</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44972</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>44998</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44998</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>44998</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44867</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45915</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45915</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44635</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45915</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45915</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45258</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45496</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45400</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45397</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44671</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44580</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45761</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45558</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44481</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45219</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45805</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45805</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45810</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45810</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45810</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>44746</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44650</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45943</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45294</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45943</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45943</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45531</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45609</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45582</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45947</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44648</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45561</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>44966</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45582</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44995</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44685</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44480</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>44480</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45461</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45183</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45611</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45835</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45835</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45604</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45180</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45155</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45839</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45611</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45968</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45842</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45971</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>44844</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45170</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45860</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44748</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45980</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45302</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45980</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45874</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45014</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45979</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45874</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45874</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45874</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45979</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45874</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45876</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>46097</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44844</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>46101</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45985</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46101</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45522</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>46048</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44867</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45985</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45168</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44601</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44543</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45049</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45520</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46113</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45016</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44596</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45635</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>44776</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45553</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>44867</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45994</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45593</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46000</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46000</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46000</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46000</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45999</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45999</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45635</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45631</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45635</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44650</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>46134</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>46136</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46136</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45183</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>46008</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>46135</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44665</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45918</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45308</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44966</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44858</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45545</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45239</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45461</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45917</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>46034</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45852</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>46036</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45242</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45397</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45860</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>46042</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45411</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45497</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45939</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45607</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>46091</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>46063</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>46148</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>46066</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46069</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>46069</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46069</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>46069</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46069</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>46071</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46072</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45474</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46073</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>46073</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46085</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46085</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46090</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>46090</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46093</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46162</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45953</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>46162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46168</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>46160</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>46181</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>46181</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46182</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>46182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>46182</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>46188</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>46191</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46191</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>46197</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>46203</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>46203</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>46205</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>46206</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>46206</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>46206</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46206</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>46206</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>46206</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>46206</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>46206</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>46219</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46223</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45196</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45196</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45196</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>46274</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45467</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46237</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46279</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>46279</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>46279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45462</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>46282</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>46240</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>46240</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>46241</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>46240</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46282</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46283</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>46241</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46241</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46148</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45335</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45868</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>46293</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>46293</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46293</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46293</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>46293</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>46293</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>46293</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46255</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>46255</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46255</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>46255</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45400</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46241</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46156</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45783</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46303</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46057</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46262</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>46303</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>46262</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>46303</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44566</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>44607</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45133</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45870</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>45923</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45413</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45078</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>44585</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>44904</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44515</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44995</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45635</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45873</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45238</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45603</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45520</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45013</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45098</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44719</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45016</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45881</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44543</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>44995</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>45474</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44727</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>46290</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>46261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44585</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45870</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44788</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45441</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45714</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45398</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45055</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45259</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>46255</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>45859</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45690</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45604</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44817</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>46241</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45442</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45986</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>45520</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>46002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45903</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>46073</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45896</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>45874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44817</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>46206</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>46006</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>46294</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44860</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45411</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45576</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44917</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>45602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44650</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45842</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45078</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45252</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45989</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45044</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>44950</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>46150</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>46149</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>46093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46280</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46297</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>46156</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45720</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44663</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44698</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44543</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44846</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44673</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44732</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44679</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44515</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44652</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44743</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44886</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44677</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44851</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>44860</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44580</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44585</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45077</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45660</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45429</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45042</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45107</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>45364</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45520</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45561</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45242</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45104</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45271</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45260</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45467</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45474</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44581</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>44543</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>44966</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45520</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44543</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45572</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44543</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>44595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45551</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45890</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45898</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45898</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45898</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45898</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45898</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>45461</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45908</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44480</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44972</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>44998</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44998</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>44998</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44867</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45915</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45915</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44635</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45915</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45915</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45258</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45929</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45496</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45400</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45397</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44671</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44580</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45761</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45558</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44481</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45219</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45805</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45805</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45810</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45810</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45810</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>44746</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44650</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45943</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45294</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45943</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45943</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45531</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45609</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45582</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45947</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44648</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45561</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>44966</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45582</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44995</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44685</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44480</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>44480</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45461</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45183</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45611</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45835</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45835</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45604</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45180</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45155</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45839</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45611</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45968</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45842</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45971</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>44844</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45170</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45860</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44748</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45980</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45302</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45980</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45874</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45014</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45979</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45874</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45874</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45874</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45979</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45874</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45876</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>46097</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44844</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>46101</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45985</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46101</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45522</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>46048</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44867</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45985</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45168</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44601</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44543</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45049</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45520</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46113</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45016</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44596</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45635</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>44776</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45553</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>44867</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45994</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45593</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46000</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46000</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46000</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46000</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45999</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45999</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45635</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45631</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45635</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44650</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>46134</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>46136</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46136</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45183</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>46008</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>46135</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>44665</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45918</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45308</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44966</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44858</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45545</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45239</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45461</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45917</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>46034</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45852</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>46036</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45242</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45397</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45860</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>46042</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45411</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45497</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45939</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45607</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>46091</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>46063</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>46148</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>46066</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46069</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>46069</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46069</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>46069</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46069</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>46071</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46072</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45474</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46073</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>46073</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46085</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>46085</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46090</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>46090</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46093</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46162</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>45953</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>46162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46168</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>46160</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>46181</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>46181</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46182</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>46182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>46182</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>46188</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>46191</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46191</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>46197</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>46203</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>46203</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>46205</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>46206</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>46206</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>46206</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46206</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>46206</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>46206</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>46206</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>46206</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>46219</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46223</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45196</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45196</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45196</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>46274</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45467</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46237</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46279</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>46279</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>46279</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45462</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>46282</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>46240</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>46240</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>46241</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>46240</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46282</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46283</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>46241</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46241</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46148</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45335</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45868</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>46293</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>46293</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46293</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46293</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>46293</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>46293</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>46293</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46255</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>46255</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46255</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>46255</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45400</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46241</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46156</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45783</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46303</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46057</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46262</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>46303</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>46262</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>46303</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44566</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>44607</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45133</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45870</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>45923</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45413</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45078</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>46167</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44585</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>44904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44515</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44995</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>46167</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>46156</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45238</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>46156</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44995</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45520</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>45098</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>45156</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>44543</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44719</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45881</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>44585</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>45233</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45016</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44543</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>44995</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45474</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>46290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>46261</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>44788</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>44817</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45870</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45714</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45441</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45398</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>46311</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45055</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>45259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45188</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>46255</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>46311</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45690</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45859</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>45725</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45604</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>46241</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45896</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>46002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45874</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>46073</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44817</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>44699</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>46206</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45442</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>45196</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>45520</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46006</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>46294</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>46311</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44860</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44698</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45411</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45044</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>46149</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45576</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45252</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44917</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45989</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>46093</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45219</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44650</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44950</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45602</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>46280</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>46286</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>46297</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>46255</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>45810</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>46311</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45842</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45525</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45791</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44488</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44663</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44698</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44846</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>44673</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>44732</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>44652</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>44515</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>44588</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44677</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44782</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44500</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44886</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>44851</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>44860</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44679</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>44743</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>44580</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44585</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45429</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44601</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44966</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>44966</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>44543</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>45561</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45260</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45660</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45474</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44543</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44648</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44543</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>44904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44665</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44867</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45364</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45461</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44844</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44635</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44858</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45302</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>44543</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44995</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44809</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45098</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45271</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45561</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45537</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>46136</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45917</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45497</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45572</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45890</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45180</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45898</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45898</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45939</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45397</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45461</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45898</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45898</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45467</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45898</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44776</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45308</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45908</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45239</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45461</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45104</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45915</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45915</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45915</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45915</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>46091</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44596</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45219</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46148</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45926</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45929</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45635</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45474</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45181</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45937</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45242</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45943</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45943</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45943</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45016</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45947</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45953</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45604</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45183</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45520</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>45611</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45611</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45971</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45522</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45968</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>46162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>46162</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44595</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45979</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45980</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45980</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>45985</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45985</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45985</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45593</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45993</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45593</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45994</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45999</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45999</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>46000</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>46000</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>46168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>46000</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>46000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45635</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>44712</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45635</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45631</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45183</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44671</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45918</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45219</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44581</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>46160</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>46034</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45520</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45520</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>46036</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45411</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>46042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44650</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>46182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>46181</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46181</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>46182</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>46182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45607</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>46063</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45042</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>46069</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>44867</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>46066</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>46069</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>46069</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46071</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46073</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>46188</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>46073</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>46072</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>46072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>44746</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>46085</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46085</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>46090</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>46090</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>46191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>46191</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>46093</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>46097</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46101</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45952</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46048</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>46101</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>46113</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45077</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45553</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>45992</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45992</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45582</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45582</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45496</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>46203</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>46203</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46135</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46134</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46134</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45107</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45860</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45545</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>46205</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>46136</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>46206</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45852</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46206</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>46206</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>46206</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46206</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>46206</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>46206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>46219</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46223</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44685</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45196</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45196</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45014</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46274</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>46279</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>46237</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>46279</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>46279</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>44845</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45462</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45467</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45551</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44650</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46240</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>46240</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>46283</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>44844</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46240</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46282</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46282</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46148</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44580</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>46241</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>46241</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>46241</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>45049</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>44904</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45609</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45242</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>44867</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46282</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44972</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46246</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46293</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46293</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46293</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>46293</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>46293</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46293</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46293</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45335</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44748</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45761</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45013</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45168</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>46255</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>44998</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>46255</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>44998</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44998</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>46255</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>46255</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>46255</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>46303</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>46303</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>46303</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45258</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46307</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46307</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>46262</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>45400</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>46307</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45397</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>46069</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>46307</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46307</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>46307</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>46307</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46262</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45558</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45565</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45805</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45805</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45810</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45810</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45810</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45294</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46310</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46311</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>46057</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45400</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45531</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45868</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>46241</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>46311</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>46311</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46311</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>46311</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>46311</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>46311</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45835</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45835</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45839</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45842</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45860</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45874</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45874</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45874</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45875</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>45874</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45874</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45876</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>44566</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45133</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>44607</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45870</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>45923</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45413</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45078</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>46167</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44585</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>44904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44515</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44995</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45952</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45992</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>46156</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>46156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45238</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>44995</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45603</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45520</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>45013</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45156</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44543</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44719</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45881</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45016</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>45992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44585</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45233</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44995</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45474</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44543</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>46261</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44817</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44788</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>45975</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45870</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44585</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44585</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45441</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>45398</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>46311</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45714</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45055</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>45259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>46255</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>46311</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45725</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45859</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44817</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45604</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>46241</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44581</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45642</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>45690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44699</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45896</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45442</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45106</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45986</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>46206</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45196</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46073</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>46311</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45903</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>46006</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46294</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45520</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44860</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44698</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45411</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45576</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45989</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>46280</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>46286</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46297</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45842</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45525</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>46311</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>46318</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>46150</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>46149</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44650</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45078</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45252</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45044</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44950</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45791</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44663</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44698</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44543</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44846</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44732</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44652</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44515</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44588</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44677</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44782</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44500</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44886</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>44851</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44860</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44679</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44585</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44580</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45888</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45042</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45890</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45898</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45898</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45898</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>44665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45898</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45898</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45903</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45908</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>46162</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45239</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45953</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>46162</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45915</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45915</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45915</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45242</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>46168</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45926</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45181</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45429</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45943</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45943</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45943</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45943</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45077</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>46160</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45946</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45660</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45946</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45946</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45947</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>46181</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>46181</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45364</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45520</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46182</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>44904</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>46182</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46182</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45242</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45467</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45271</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45611</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45604</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45260</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>46191</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45611</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45971</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>46197</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44712</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45980</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45980</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45979</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>46203</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45979</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>46203</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44543</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>46205</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45985</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45985</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45551</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46206</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>46206</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45985</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>46206</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>46206</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46206</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46206</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>46206</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46206</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>46206</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45593</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45474</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45993</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45994</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45593</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>46000</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>46219</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>46000</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>46000</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>44972</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45999</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45631</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45635</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44998</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44998</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>46223</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44998</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45196</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45196</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45183</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>46008</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45467</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46237</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>46279</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46279</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>45462</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45918</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>46282</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>46282</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>46282</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45258</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>46240</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>46240</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>46241</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46240</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46282</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46283</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>44581</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>46241</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>46241</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44543</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46042</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46246</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45400</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45397</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45411</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45558</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45565</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44966</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45805</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45805</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45607</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45335</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45810</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45810</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46293</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>46293</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45294</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>46293</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46063</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45531</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>46066</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>46293</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46293</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46069</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46293</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>46069</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>46293</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>46069</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>46071</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>46072</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46072</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>46073</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>46073</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46085</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>46085</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>46255</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>44595</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45835</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45835</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>46090</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>46090</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46255</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>46097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45537</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45842</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>46255</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>46255</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>46255</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>46101</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>46101</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>46048</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45860</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>46113</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>46303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45874</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46303</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45874</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45874</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45874</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45874</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>46303</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45876</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45875</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>46307</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>46307</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46307</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>46134</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>46134</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>46262</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44867</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46262</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>46136</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46136</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>44635</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46307</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46307</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46307</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>46310</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>46135</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45308</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45400</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>46311</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>46311</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45545</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46311</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46311</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45461</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>46057</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45868</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>46311</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45852</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45013</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>46311</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>46311</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45397</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>45860</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45497</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45496</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45939</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44671</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>46307</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46317</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>46241</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46274</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45761</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>46091</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>46148</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45474</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
         <v>44746</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45609</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45582</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>45582</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45461</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45170</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44867</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45168</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>44601</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>44543</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45049</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45520</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45016</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44596</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45635</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44809</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45107</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45561</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45104</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45520</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>44543</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45461</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>44580</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45219</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44650</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>44648</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45561</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>44685</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45180</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45155</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>44904</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44844</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>44845</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44748</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45302</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45014</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44844</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45522</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>44776</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45553</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>44867</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44650</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44566</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>44607</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45133</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>

--- a/Översikt STORUMAN.xlsx
+++ b/Översikt STORUMAN.xlsx
@@ -601,7 +601,7 @@
         <v>45870</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>45923</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45413</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45078</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>46167</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44585</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>44904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>44515</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44995</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45952</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45992</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>46156</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>46156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45238</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>44995</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45603</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45520</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45098</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>45013</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45156</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44543</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44719</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45881</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45016</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>45992</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44585</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45233</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44995</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45474</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44543</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>46261</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44817</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44788</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>45975</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45870</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44585</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44585</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45441</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>45398</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>46311</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45714</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45055</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>45259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>46255</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>46311</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45725</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45859</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44817</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45604</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>46241</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44581</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45642</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>45690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44699</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45896</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45442</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45106</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45986</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>46206</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45196</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>46073</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>46311</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45903</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>46006</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>46294</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45520</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44860</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44698</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45411</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45576</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45989</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>46280</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>46286</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45810</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46297</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45842</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45525</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>46311</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>46318</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>46150</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>46149</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44650</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45078</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45252</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45044</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44950</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45791</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44663</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44698</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44543</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44846</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44732</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44652</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44515</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44588</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44677</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44782</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44500</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44886</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>44851</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44860</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44679</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44585</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44580</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45888</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45042</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45890</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45898</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45898</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45898</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>44665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45898</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45898</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45903</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45908</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>46162</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45239</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45953</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>46162</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45915</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45915</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45915</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45242</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>46168</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45926</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45181</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45429</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45943</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45943</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45943</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45943</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45077</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>46160</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45946</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45660</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45946</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45946</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45947</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>46181</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>46181</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45364</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45520</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46182</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>44904</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>46182</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46182</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45242</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45467</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45271</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45611</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45604</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45260</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>46191</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45611</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45971</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>46197</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44712</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45980</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45980</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45979</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>46203</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45979</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>46203</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44543</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>46205</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45985</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45985</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45551</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46206</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>46206</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45985</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>46206</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>46206</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46206</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46206</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>46206</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46206</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>46206</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45593</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45474</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45993</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45994</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45593</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>46000</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>46219</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>46000</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>46000</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>44972</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45999</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45631</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45635</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44998</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44998</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>46223</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44998</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45196</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45196</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45183</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>46008</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45467</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46237</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>46279</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46279</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>45462</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45918</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>46282</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>46282</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>46282</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45258</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>46240</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>46240</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>46241</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46240</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46282</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46283</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>44581</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>46241</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>46241</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44543</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46042</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46246</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45400</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45397</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45411</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45558</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45565</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44966</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45805</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45805</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45607</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45335</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45810</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45810</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46293</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>46293</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45294</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>46293</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46063</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45531</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>46066</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>46293</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46293</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46069</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46293</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>46069</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>46293</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>46069</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>46071</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>46072</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46072</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>46073</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>46073</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46085</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>46085</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>46255</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>44595</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45835</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45835</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>46090</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>46090</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46255</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>46097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45537</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45842</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>46255</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>46255</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>46255</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>46101</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>46101</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>46048</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45860</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>46113</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>46303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45874</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46303</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45874</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45874</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45874</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45874</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>46303</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45876</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45875</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>46307</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>46307</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46307</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>46134</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>46134</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>46262</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44867</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46262</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>46136</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46136</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>44635</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46307</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46307</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46307</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>46310</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>46135</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45308</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45400</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>46311</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>46311</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45545</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46311</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46311</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45461</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>46057</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45868</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>46311</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45852</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45013</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>46311</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>46311</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45397</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>45860</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45497</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45496</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45939</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44671</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>46307</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46317</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>46241</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46274</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45761</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>46091</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>46148</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45474</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
         <v>44746</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45609</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45582</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>45582</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45461</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45170</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44867</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45168</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>44601</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>44543</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45049</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45520</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45016</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44596</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45635</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44809</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45107</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45561</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45104</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45520</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>44543</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45461</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>44580</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45219</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44650</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>44648</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45561</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>44685</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45180</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45155</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>44904</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44844</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>44845</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44748</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45302</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45014</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44844</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45522</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>44776</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45553</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>44867</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44650</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44566</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>44607</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45133</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
